--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2023_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2023_biobio.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 19:43</t>
+    <t xml:space="preserve">2026-09-09 22:30</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2023_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2023_biobio.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 22:30</t>
+    <t xml:space="preserve">2026-09-12 19:46</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2023_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2023_biobio.xlsx
@@ -36,102 +36,102 @@
     <t xml:space="preserve">Biobío</t>
   </si>
   <si>
+    <t xml:space="preserve">Hualpén</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chiguayante</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Santa Juana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hualqui</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Negrete</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Florida</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Los Alamos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tucapel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Curanilahue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cabrero</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Penco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mulchén</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Laja</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Santa Bárbara</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yumbel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alto Biobío</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tomé</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arauco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quilaco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cañete</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Contulmo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quilleco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coronel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tirúa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Rosendo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nacimiento</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Antuco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lebu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lota</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Los Angeles</t>
+  </si>
+  <si>
     <t xml:space="preserve">San Pedro de la Paz</t>
   </si>
   <si>
-    <t xml:space="preserve">Los Angeles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hualqui</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Los Alamos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Florida</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cabrero</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yumbel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Santa Juana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tucapel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coronel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Negrete</t>
-  </si>
-  <si>
     <t xml:space="preserve">Concepción</t>
   </si>
   <si>
-    <t xml:space="preserve">Cañete</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mulchén</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tomé</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quilaco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Arauco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quilleco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Contulmo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Laja</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Santa Bárbara</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alto Biobío</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Antuco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tirúa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">San Rosendo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Curanilahue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lebu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nacimiento</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Penco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chiguayante</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hualpén</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lota</t>
-  </si>
-  <si>
     <t xml:space="preserve">Talcahuano</t>
   </si>
   <si>
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-12 19:46</t>
+    <t xml:space="preserve">2026-09-24 00:24</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -568,13 +568,13 @@
         <v>6</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>8108</v>
+        <v>8112</v>
       </c>
       <c r="D2" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>3250</v>
+        <v>2207</v>
       </c>
     </row>
     <row r="3">
@@ -585,13 +585,13 @@
         <v>7</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>8301</v>
+        <v>8103</v>
       </c>
       <c r="D3" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>3039</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="4">
@@ -602,13 +602,13 @@
         <v>8</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>8105</v>
+        <v>8109</v>
       </c>
       <c r="D4" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>2222</v>
+        <v>831</v>
       </c>
     </row>
     <row r="5">
@@ -619,13 +619,13 @@
         <v>9</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>8206</v>
+        <v>8105</v>
       </c>
       <c r="D5" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>1808</v>
+        <v>822</v>
       </c>
     </row>
     <row r="6">
@@ -636,13 +636,13 @@
         <v>10</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>8104</v>
+        <v>8307</v>
       </c>
       <c r="D6" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>1679</v>
+        <v>803</v>
       </c>
     </row>
     <row r="7">
@@ -653,13 +653,13 @@
         <v>11</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>8303</v>
+        <v>8104</v>
       </c>
       <c r="D7" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>1524</v>
+        <v>598</v>
       </c>
     </row>
     <row r="8">
@@ -670,13 +670,13 @@
         <v>12</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>8313</v>
+        <v>8206</v>
       </c>
       <c r="D8" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>1522</v>
+        <v>512</v>
       </c>
     </row>
     <row r="9">
@@ -687,13 +687,13 @@
         <v>13</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>8109</v>
+        <v>8312</v>
       </c>
       <c r="D9" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>1502</v>
+        <v>458</v>
       </c>
     </row>
     <row r="10">
@@ -704,13 +704,13 @@
         <v>14</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>8312</v>
+        <v>8205</v>
       </c>
       <c r="D10" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>1422</v>
+        <v>433</v>
       </c>
     </row>
     <row r="11">
@@ -721,13 +721,13 @@
         <v>15</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>8102</v>
+        <v>8303</v>
       </c>
       <c r="D11" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>1207</v>
+        <v>432</v>
       </c>
     </row>
     <row r="12">
@@ -738,13 +738,13 @@
         <v>16</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>8307</v>
+        <v>8107</v>
       </c>
       <c r="D12" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>1137</v>
+        <v>420</v>
       </c>
     </row>
     <row r="13">
@@ -755,13 +755,13 @@
         <v>17</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>8101</v>
+        <v>8305</v>
       </c>
       <c r="D13" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>1136</v>
+        <v>415</v>
       </c>
     </row>
     <row r="14">
@@ -772,13 +772,13 @@
         <v>18</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>8203</v>
+        <v>8304</v>
       </c>
       <c r="D14" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>863</v>
+        <v>405</v>
       </c>
     </row>
     <row r="15">
@@ -789,13 +789,13 @@
         <v>19</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>8305</v>
+        <v>8311</v>
       </c>
       <c r="D15" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>861</v>
+        <v>330</v>
       </c>
     </row>
     <row r="16">
@@ -806,13 +806,13 @@
         <v>20</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>8111</v>
+        <v>8313</v>
       </c>
       <c r="D16" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>812</v>
+        <v>327</v>
       </c>
     </row>
     <row r="17">
@@ -823,13 +823,13 @@
         <v>21</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>8308</v>
+        <v>8314</v>
       </c>
       <c r="D17" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>617</v>
+        <v>215</v>
       </c>
     </row>
     <row r="18">
@@ -840,13 +840,13 @@
         <v>22</v>
       </c>
       <c r="C18" s="2" t="n">
-        <v>8202</v>
+        <v>8111</v>
       </c>
       <c r="D18" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>537</v>
+        <v>180</v>
       </c>
     </row>
     <row r="19">
@@ -857,13 +857,13 @@
         <v>23</v>
       </c>
       <c r="C19" s="2" t="n">
-        <v>8309</v>
+        <v>8202</v>
       </c>
       <c r="D19" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>522</v>
+        <v>179</v>
       </c>
     </row>
     <row r="20">
@@ -874,13 +874,13 @@
         <v>24</v>
       </c>
       <c r="C20" s="2" t="n">
-        <v>8204</v>
+        <v>8308</v>
       </c>
       <c r="D20" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>479</v>
+        <v>161</v>
       </c>
     </row>
     <row r="21">
@@ -891,13 +891,13 @@
         <v>25</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>8304</v>
+        <v>8203</v>
       </c>
       <c r="D21" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>455</v>
+        <v>138</v>
       </c>
     </row>
     <row r="22">
@@ -908,13 +908,13 @@
         <v>26</v>
       </c>
       <c r="C22" s="2" t="n">
-        <v>8311</v>
+        <v>8204</v>
       </c>
       <c r="D22" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>307</v>
+        <v>134</v>
       </c>
     </row>
     <row r="23">
@@ -925,13 +925,13 @@
         <v>27</v>
       </c>
       <c r="C23" s="2" t="n">
-        <v>8314</v>
+        <v>8309</v>
       </c>
       <c r="D23" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>269</v>
+        <v>118</v>
       </c>
     </row>
     <row r="24">
@@ -942,13 +942,13 @@
         <v>28</v>
       </c>
       <c r="C24" s="2" t="n">
-        <v>8302</v>
+        <v>8102</v>
       </c>
       <c r="D24" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>245</v>
+        <v>98</v>
       </c>
     </row>
     <row r="25">
@@ -965,7 +965,7 @@
         <v>2023</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>118</v>
+        <v>70</v>
       </c>
     </row>
     <row r="26">
@@ -982,7 +982,7 @@
         <v>2023</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="27">
@@ -993,13 +993,13 @@
         <v>31</v>
       </c>
       <c r="C27" s="2" t="n">
-        <v>8205</v>
+        <v>8306</v>
       </c>
       <c r="D27" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>-34</v>
+        <v>27</v>
       </c>
     </row>
     <row r="28">
@@ -1010,13 +1010,13 @@
         <v>32</v>
       </c>
       <c r="C28" s="2" t="n">
-        <v>8201</v>
+        <v>8302</v>
       </c>
       <c r="D28" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>-135</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="29">
@@ -1027,13 +1027,13 @@
         <v>33</v>
       </c>
       <c r="C29" s="2" t="n">
-        <v>8306</v>
+        <v>8201</v>
       </c>
       <c r="D29" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>-272</v>
+        <v>-32</v>
       </c>
     </row>
     <row r="30">
@@ -1044,13 +1044,13 @@
         <v>34</v>
       </c>
       <c r="C30" s="2" t="n">
-        <v>8107</v>
+        <v>8106</v>
       </c>
       <c r="D30" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>-1097</v>
+        <v>-321</v>
       </c>
     </row>
     <row r="31">
@@ -1061,13 +1061,13 @@
         <v>35</v>
       </c>
       <c r="C31" s="2" t="n">
-        <v>8103</v>
+        <v>8301</v>
       </c>
       <c r="D31" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>-1389</v>
+        <v>-523</v>
       </c>
     </row>
     <row r="32">
@@ -1078,13 +1078,13 @@
         <v>36</v>
       </c>
       <c r="C32" s="2" t="n">
-        <v>8112</v>
+        <v>8108</v>
       </c>
       <c r="D32" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>-1958</v>
+        <v>-704</v>
       </c>
     </row>
     <row r="33">
@@ -1095,13 +1095,13 @@
         <v>37</v>
       </c>
       <c r="C33" s="2" t="n">
-        <v>8106</v>
+        <v>8101</v>
       </c>
       <c r="D33" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>-2636</v>
+        <v>-3158</v>
       </c>
     </row>
     <row r="34">
@@ -1118,7 +1118,7 @@
         <v>2023</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>-6770</v>
+        <v>-3873</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2023_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2023_biobio.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:24</t>
+    <t xml:space="preserve">2026-09-27 22:13</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2023_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2023_biobio.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 22:13</t>
+    <t xml:space="preserve">2026-10-01 20:54</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2023_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2023_biobio.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 20:54</t>
+    <t xml:space="preserve">2026-10-02 13:19</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2023_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2023_biobio.xlsx
@@ -54,7 +54,7 @@
     <t xml:space="preserve">Florida</t>
   </si>
   <si>
-    <t xml:space="preserve">Los Alamos</t>
+    <t xml:space="preserve">Los Álamos</t>
   </si>
   <si>
     <t xml:space="preserve">Tucapel</t>
@@ -123,7 +123,7 @@
     <t xml:space="preserve">Lota</t>
   </si>
   <si>
-    <t xml:space="preserve">Los Angeles</t>
+    <t xml:space="preserve">Los Ángeles</t>
   </si>
   <si>
     <t xml:space="preserve">San Pedro de la Paz</t>
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 13:19</t>
+    <t xml:space="preserve">2026-10-04 08:08</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2023_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2023_biobio.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 08:08</t>
+    <t xml:space="preserve">2026-10-05 08:01</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
